--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486350_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486350_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7404</v>
+        <v>8.0863</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5316</v>
+        <v>7.6001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2088</v>
+        <v>0.4862</v>
       </c>
       <c r="G2" t="n">
         <v>5.52</v>
@@ -610,13 +610,13 @@
         <v>2.8276</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1696</v>
+        <v>0.1763</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1286</v>
+        <v>0.1971</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2981</v>
+        <v>-0.0207</v>
       </c>
       <c r="V2" t="n">
         <v>2.8249</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2796</v>
+        <v>3.9713</v>
       </c>
       <c r="E3" t="n">
         <v>4.6441</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3645</v>
+        <v>-0.6727</v>
       </c>
       <c r="G3" t="n">
         <v>1.3054</v>
@@ -688,13 +688,13 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>1.257</v>
+        <v>0.9487</v>
       </c>
       <c r="T3" t="n">
         <v>0.4711</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7859</v>
+        <v>0.4777</v>
       </c>
       <c r="V3" t="n">
         <v>1.4997</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1757</v>
+        <v>3.0014</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7009</v>
+        <v>2.4341</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4748</v>
+        <v>0.5673</v>
       </c>
       <c r="G4" t="n">
         <v>0.6791</v>
@@ -766,13 +766,13 @@
         <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4967</v>
+        <v>0.3224</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4711</v>
+        <v>0.2043</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0256</v>
+        <v>0.1181</v>
       </c>
       <c r="V4" t="n">
         <v>1.13</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0704</v>
+        <v>2.6349</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5953</v>
+        <v>1.0365</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4752</v>
+        <v>1.5985</v>
       </c>
       <c r="G5" t="n">
         <v>-0.1847</v>
@@ -844,13 +844,13 @@
         <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9522</v>
+        <v>0.5167</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0106</v>
+        <v>0.4518</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0584</v>
+        <v>0.0649</v>
       </c>
       <c r="V5" t="n">
         <v>2.0854</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. LOPEZ BARRANTES</t>
+          <t>S. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6303</v>
+        <v>2.17</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1158</v>
+        <v>0.833</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5145999999999999</v>
+        <v>1.3369</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9829</v>
+        <v>0.5755</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6666</v>
+        <v>-0.6022</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3163</v>
+        <v>1.1778</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0077</v>
+        <v>2.1773</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2045</v>
+        <v>-0.2523</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8032</v>
+        <v>2.4296</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0248</v>
+        <v>-1.6018</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4621</v>
+        <v>-0.3499</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4869</v>
+        <v>-1.2519</v>
       </c>
       <c r="P6" t="n">
         <v>0.2175</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>1.305</v>
+        <v>2.3926</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6251</v>
+        <v>0.2469</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8051</v>
+        <v>-0.2992</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.18</v>
+        <v>0.5462</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. GARCIA CALVO</t>
+          <t>H. LOPEZ BARRANTES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4897</v>
+        <v>1.6699</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7212</v>
+        <v>1.4019</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7685</v>
+        <v>0.268</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5755</v>
+        <v>1.9829</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6022</v>
+        <v>1.6666</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1778</v>
+        <v>0.3163</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1773</v>
+        <v>2.0077</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2523</v>
+        <v>1.2045</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4296</v>
+        <v>0.8032</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6018</v>
+        <v>-0.0248</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3499</v>
+        <v>0.4621</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2519</v>
+        <v>-0.4869</v>
       </c>
       <c r="P7" t="n">
         <v>0.2175</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3926</v>
+        <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5667</v>
+        <v>-0.3353</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.411</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9777</v>
+        <v>-0.4266</v>
       </c>
       <c r="V7" t="n">
-        <v>1.13</v>
+        <v>-0.1952</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>0.3904</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5857</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2212</v>
+        <v>0.282</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0693</v>
+        <v>2.9143</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8481</v>
+        <v>-2.6323</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -1078,13 +1078,13 @@
         <v>2.3926</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7586000000000001</v>
+        <v>-0.6979</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.1634</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7502</v>
+        <v>-0.5345</v>
       </c>
       <c r="V8" t="n">
         <v>-1.3252</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8427</v>
+        <v>-0.4766</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6812</v>
+        <v>1.0165</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5239</v>
+        <v>-1.493</v>
       </c>
       <c r="G9" t="n">
         <v>0.1628</v>
@@ -1156,13 +1156,13 @@
         <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.918</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3425</v>
+        <v>-0.0072</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5755</v>
+        <v>-0.5447</v>
       </c>
       <c r="V9" t="n">
         <v>0.5649999999999999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.452</v>
+        <v>-0.5473</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5656</v>
+        <v>1.1929</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0177</v>
+        <v>-1.7402</v>
       </c>
       <c r="G10" t="n">
         <v>1.181</v>
@@ -1234,13 +1234,13 @@
         <v>2.8276</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9831</v>
+        <v>-0.0784</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.0577</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2981</v>
+        <v>-0.0207</v>
       </c>
       <c r="V10" t="n">
         <v>-3.3899</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3305</v>
+        <v>-1.9953</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.703</v>
+        <v>-0.3677</v>
       </c>
       <c r="F11" t="n">
         <v>-1.6276</v>
@@ -1312,10 +1312,10 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8136</v>
+        <v>-0.4783</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.411</v>
+        <v>-0.0757</v>
       </c>
       <c r="U11" t="n">
         <v>-0.4026</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0428</v>
+        <v>-2.5148</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2583</v>
+        <v>-0.6996</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7844</v>
+        <v>-1.8152</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6627</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1201</v>
+        <v>-0.5921</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.548</v>
+        <v>0.0108</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-0.603</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.9393</v>
+        <v>16.2818</v>
       </c>
       <c r="E13" t="n">
-        <v>21.6637</v>
+        <v>22.0061</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.724299999999999</v>
+        <v>-5.7241</v>
       </c>
       <c r="G13" t="n">
         <v>8.3675</v>
@@ -1468,13 +1468,13 @@
         <v>18.488</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8653000000000001</v>
+        <v>-0.5228999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4805999999999999</v>
+        <v>0.8232</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3458</v>
+        <v>-1.3459</v>
       </c>
       <c r="V13" t="n">
         <v>2.9995</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.9413</v>
+        <v>4.5366</v>
       </c>
       <c r="E14" t="n">
-        <v>9.3302</v>
+        <v>8.7714</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.3889</v>
+        <v>-4.2348</v>
       </c>
       <c r="G14" t="n">
         <v>2.301</v>
@@ -1546,13 +1546,13 @@
         <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0547</v>
+        <v>-0.4593</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6682</v>
+        <v>0.1094</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7228</v>
+        <v>-0.5687</v>
       </c>
       <c r="V14" t="n">
         <v>2.2599</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0272</v>
+        <v>3.5976</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0339</v>
+        <v>3.4809</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0066</v>
+        <v>0.1167</v>
       </c>
       <c r="G15" t="n">
         <v>2.373</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2158</v>
+        <v>0.3545</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1935</v>
+        <v>0.2536</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0224</v>
+        <v>0.1009</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6726</v>
+        <v>1.4799</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9656</v>
+        <v>2.7421</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.293</v>
+        <v>-1.2622</v>
       </c>
       <c r="G16" t="n">
         <v>1.9843</v>
@@ -1702,13 +1702,13 @@
         <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3186</v>
+        <v>0.1259</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4026</v>
+        <v>0.1791</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0532</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1952</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. TERINS</t>
+          <t>J. BROWN-FERGUSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6267</v>
+        <v>0.9819</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6453</v>
+        <v>1.5147</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0186</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2039</v>
+        <v>0.3709</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2342</v>
+        <v>0.6203</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0303</v>
+        <v>-0.2494</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7963</v>
+        <v>1.8867</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5141</v>
+        <v>1.7337</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2822</v>
+        <v>0.153</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0003</v>
+        <v>-1.5158</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7484</v>
+        <v>-1.1134</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2519</v>
+        <v>-0.4024</v>
       </c>
       <c r="P17" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9606</v>
+        <v>-0.6717</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1935</v>
+        <v>-0.3497</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1541</v>
+        <v>-0.3221</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BROWN-FERGUSON</t>
+          <t>F. TERINS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5233</v>
+        <v>0.2453</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1794</v>
+        <v>1.757</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6561</v>
+        <v>-1.5117</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3709</v>
+        <v>-0.2039</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6203</v>
+        <v>-0.2342</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2494</v>
+        <v>0.0303</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8867</v>
+        <v>1.7963</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7337</v>
+        <v>0.5141</v>
       </c>
       <c r="L18" t="n">
-        <v>0.153</v>
+        <v>1.2822</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5158</v>
+        <v>-2.0003</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1134</v>
+        <v>-0.7484</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4024</v>
+        <v>-1.2519</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1303</v>
+        <v>0.5792</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4454</v>
+        <v>0.6609</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1952</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PARRADO CALABRIA</t>
+          <t>G. JOFRESA SARRET</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0191</v>
+        <v>-1.4223</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4183</v>
+        <v>-0.6872</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4374</v>
+        <v>-0.7351</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9639</v>
+        <v>-2.4482</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.736</v>
+        <v>-1.323</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2279</v>
+        <v>-1.1252</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2014</v>
+        <v>0.0525</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2618</v>
+        <v>-0.5411</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9395</v>
+        <v>0.5937</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1652</v>
+        <v>-2.5007</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9978</v>
+        <v>-0.7819</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1674</v>
+        <v>-1.7188</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.0451</v>
+        <v>0.6525</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.5676</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>1.295</v>
+        <v>0.1782</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6992</v>
+        <v>0.1526</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4043</v>
+        <v>0.0255</v>
       </c>
       <c r="V19" t="n">
-        <v>1.695</v>
+        <v>0.1952</v>
       </c>
       <c r="W19" t="n">
-        <v>2.0854</v>
+        <v>0.1952</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. VILA SOLEY</t>
+          <t>A. PARRADO CALABRIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1068</v>
+        <v>-1.7282</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7861</v>
+        <v>-0.4757</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8928</v>
+        <v>-1.2525</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.744</v>
+        <v>-0.9639</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0489</v>
+        <v>-0.736</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7929</v>
+        <v>-0.2279</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2348</v>
+        <v>1.2014</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3933</v>
+        <v>0.2618</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8415</v>
+        <v>0.9395</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.9788</v>
+        <v>-2.1652</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3444</v>
+        <v>-0.9978</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6344</v>
+        <v>-1.1674</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.9576</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.2626</v>
+        <v>-4.5676</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>1.7248</v>
+        <v>0.5858</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6187</v>
+        <v>0.8051</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1061</v>
+        <v>-0.2193</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.13</v>
+        <v>1.695</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1952</v>
+        <v>2.0854</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3252</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. JOFRESA SARRET</t>
+          <t>G. GIL GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1622</v>
+        <v>-2.6307</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5812</v>
+        <v>0.674</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.581</v>
+        <v>-3.3046</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4482</v>
+        <v>-1.0524</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.323</v>
+        <v>-0.4746</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1252</v>
+        <v>-0.5777</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0525</v>
+        <v>1.2969</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5411</v>
+        <v>0.0912</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5937</v>
+        <v>1.2057</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5007</v>
+        <v>-2.3493</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7819</v>
+        <v>-0.5659</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7188</v>
+        <v>-1.7834</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5618</v>
+        <v>0.0514</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7413999999999999</v>
+        <v>0.1166</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1796</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1952</v>
+        <v>-2.0647</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1952</v>
+        <v>-0.7395</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. GIL GARCIA</t>
+          <t>R. VILA SOLEY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9853</v>
+        <v>-3.0201</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2269</v>
+        <v>-0.2197</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2122</v>
+        <v>-2.8004</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0524</v>
+        <v>-0.744</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4746</v>
+        <v>0.0489</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5777</v>
+        <v>-0.7929</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2969</v>
+        <v>2.2348</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0912</v>
+        <v>1.3933</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2057</v>
+        <v>0.8415</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.3493</v>
+        <v>-2.9788</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5659</v>
+        <v>-1.3444</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.7834</v>
+        <v>-1.6344</v>
       </c>
       <c r="P22" t="n">
-        <v>0.435</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R22" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3032</v>
+        <v>0.8114</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3305</v>
+        <v>0.6129</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0273</v>
+        <v>0.1986</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.0647</v>
+        <v>-1.13</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7395</v>
+        <v>0.1952</v>
       </c>
       <c r="X22" t="n">
         <v>-1.3252</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4911</v>
+        <v>-3.256</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1969</v>
+        <v>-2.0851</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2942</v>
+        <v>-1.1709</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2993</v>
@@ -2248,13 +2248,13 @@
         <v>0.435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4093</v>
+        <v>-0.1742</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3425</v>
+        <v>-0.2307</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0668</v>
+        <v>0.0565</v>
       </c>
       <c r="V23" t="n">
         <v>-1.13</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4488</v>
+        <v>-4.1944</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5759</v>
+        <v>-2.3524</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8729</v>
+        <v>-1.8421</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3253</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6884</v>
+        <v>-0.4341</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.411</v>
+        <v>-0.1875</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2775</v>
+        <v>-0.2466</v>
       </c>
       <c r="V24" t="n">
         <v>-1.13</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.5174</v>
+        <v>-10.5289</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.5075</v>
+        <v>-7.3957</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.0099</v>
+        <v>-3.1332</v>
       </c>
       <c r="G25" t="n">
         <v>-7.3597</v>
@@ -2404,13 +2404,13 @@
         <v>1.5225</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0702</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1454</v>
+        <v>-0.0336</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0752</v>
+        <v>-0.0481</v>
       </c>
       <c r="V25" t="n">
         <v>-1.13</v>
@@ -2437,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-15.9396</v>
+        <v>-15.9393</v>
       </c>
       <c r="E26" t="n">
-        <v>5.724200000000003</v>
+        <v>5.724300000000001</v>
       </c>
       <c r="F26" t="n">
         <v>-21.6636</v>
@@ -2458,7 +2458,7 @@
         <v>15.2849</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1085000000000003</v>
+        <v>0.1084999999999994</v>
       </c>
       <c r="L26" t="n">
         <v>15.1764</v>
@@ -2482,19 +2482,19 @@
         <v>13.0502</v>
       </c>
       <c r="S26" t="n">
-        <v>0.8653000000000003</v>
+        <v>0.8654000000000003</v>
       </c>
       <c r="T26" t="n">
-        <v>1.345900000000001</v>
+        <v>1.3461</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4809000000000003</v>
+        <v>-0.4807999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-2.9996</v>
       </c>
       <c r="W26" t="n">
-        <v>7.5814</v>
+        <v>7.581399999999999</v>
       </c>
       <c r="X26" t="n">
         <v>-10.581</v>
